--- a/control_datos_email.xlsx
+++ b/control_datos_email.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Mercadotecnia/Desktop/automatizacióncorreos/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBDEC685-44FC-CA40-B68B-2F51FBC2CF42}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C70BCD1D-2674-9742-8FC5-7B22835BA823}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17160" yWindow="3820" windowWidth="27640" windowHeight="16120" xr2:uid="{66D09105-B21B-F042-BD54-AE668A6F427D}"/>
+    <workbookView xWindow="16660" yWindow="4440" windowWidth="27640" windowHeight="16120" xr2:uid="{66D09105-B21B-F042-BD54-AE668A6F427D}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -15163,7 +15163,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -15180,6 +15180,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -15207,10 +15223,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -15525,7 +15543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B26AC2-51D3-AF4C-8667-F688036C73A4}">
-  <dimension ref="A1:D1714"/>
+  <dimension ref="A1:E1714"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23" customWidth="1"/>
@@ -29660,7 +29678,7 @@
         <v>3884</v>
       </c>
     </row>
-    <row r="1281" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1281" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1281" s="2" t="s">
         <v>3885</v>
       </c>
@@ -29671,7 +29689,7 @@
         <v>3887</v>
       </c>
     </row>
-    <row r="1282" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1282" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1282" s="2" t="s">
         <v>3888</v>
       </c>
@@ -29682,7 +29700,7 @@
         <v>3890</v>
       </c>
     </row>
-    <row r="1283" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1283" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1283" s="2" t="s">
         <v>3891</v>
       </c>
@@ -29693,7 +29711,7 @@
         <v>3893</v>
       </c>
     </row>
-    <row r="1284" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1284" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1284" s="2" t="s">
         <v>3894</v>
       </c>
@@ -29704,7 +29722,7 @@
         <v>3896</v>
       </c>
     </row>
-    <row r="1285" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1285" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1285" s="2" t="s">
         <v>3897</v>
       </c>
@@ -29715,7 +29733,7 @@
         <v>3899</v>
       </c>
     </row>
-    <row r="1286" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1286" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1286" s="2" t="s">
         <v>3900</v>
       </c>
@@ -29726,7 +29744,7 @@
         <v>3902</v>
       </c>
     </row>
-    <row r="1287" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1287" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1287" s="2" t="s">
         <v>3903</v>
       </c>
@@ -29737,7 +29755,7 @@
         <v>3905</v>
       </c>
     </row>
-    <row r="1288" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1288" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1288" s="2" t="s">
         <v>3906</v>
       </c>
@@ -29748,7 +29766,7 @@
         <v>3908</v>
       </c>
     </row>
-    <row r="1289" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1289" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1289" s="2" t="s">
         <v>3909</v>
       </c>
@@ -29758,8 +29776,9 @@
       <c r="C1289" s="2" t="s">
         <v>3911</v>
       </c>
-    </row>
-    <row r="1290" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E1289" s="4"/>
+    </row>
+    <row r="1290" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1290" s="2" t="s">
         <v>3912</v>
       </c>
@@ -29770,7 +29789,7 @@
         <v>3914</v>
       </c>
     </row>
-    <row r="1291" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1291" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1291" s="2" t="s">
         <v>3915</v>
       </c>
@@ -29781,7 +29800,7 @@
         <v>3917</v>
       </c>
     </row>
-    <row r="1292" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1292" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1292" s="2" t="s">
         <v>3918</v>
       </c>
@@ -29792,7 +29811,7 @@
         <v>3920</v>
       </c>
     </row>
-    <row r="1293" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1293" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1293" s="2" t="s">
         <v>3921</v>
       </c>
@@ -29803,7 +29822,7 @@
         <v>3923</v>
       </c>
     </row>
-    <row r="1294" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1294" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1294" s="2" t="s">
         <v>3924</v>
       </c>
@@ -29814,7 +29833,7 @@
         <v>3926</v>
       </c>
     </row>
-    <row r="1295" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1295" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1295" s="2" t="s">
         <v>3927</v>
       </c>
@@ -29825,7 +29844,7 @@
         <v>3929</v>
       </c>
     </row>
-    <row r="1296" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1296" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1296" s="2" t="s">
         <v>3930</v>
       </c>
@@ -34259,7 +34278,7 @@
       </c>
     </row>
     <row r="1699" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A1699" s="2" t="s">
+      <c r="A1699" s="3" t="s">
         <v>92</v>
       </c>
       <c r="B1699" s="2" t="s">
